--- a/artfynd/A 57570-2023 artfynd.xlsx
+++ b/artfynd/A 57570-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,56 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68880704</v>
+        <v>137493653</v>
       </c>
       <c r="B2" t="n">
-        <v>58067</v>
+        <v>96748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100090</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S. Timmerö 300 m V, Ög</t>
+          <t>Lillån, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503330</v>
+        <v>503442</v>
       </c>
       <c r="R2" t="n">
-        <v>6447366</v>
+        <v>6447554</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,16 +765,231 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Josefsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Josefsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137493653</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137494107</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96737</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillån, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>503441</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6447554</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boxholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ekeby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137494107</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>68880704</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58067</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S. Timmerö 300 m V, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>503330</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6447366</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boxholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ekeby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-08-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-08-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Josefsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Josefsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/68880704</t>
         </is>
@@ -794,6 +998,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57570-2023 artfynd.xlsx
+++ b/artfynd/A 57570-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137493653</v>
       </c>
       <c r="B2" t="n">
-        <v>96748</v>
+        <v>96752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137494107</v>
       </c>
       <c r="B3" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
